--- a/output/yearly_population_iteration_9_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_9_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5096</v>
+        <v>8825</v>
       </c>
       <c r="C2" t="n">
-        <v>11862</v>
+        <v>5800</v>
       </c>
       <c r="D2" t="n">
-        <v>31473</v>
+        <v>26768</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2799</v>
+        <v>5097</v>
       </c>
       <c r="C3" t="n">
-        <v>5620</v>
+        <v>5234</v>
       </c>
       <c r="D3" t="n">
-        <v>18203</v>
+        <v>11790</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2181</v>
+        <v>3572</v>
       </c>
       <c r="C4" t="n">
-        <v>6001</v>
+        <v>6483</v>
       </c>
       <c r="D4" t="n">
-        <v>8517</v>
+        <v>5281</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1480</v>
+        <v>2216</v>
       </c>
       <c r="C5" t="n">
-        <v>4884</v>
+        <v>4676</v>
       </c>
       <c r="D5" t="n">
-        <v>3223</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>846</v>
+        <v>1268</v>
       </c>
       <c r="C6" t="n">
-        <v>3214</v>
+        <v>2051</v>
       </c>
       <c r="D6" t="n">
-        <v>1255</v>
+        <v>964</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>396</v>
+        <v>630</v>
       </c>
       <c r="C7" t="n">
-        <v>1695</v>
+        <v>1041</v>
       </c>
       <c r="D7" t="n">
-        <v>669</v>
+        <v>632</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>238</v>
       </c>
       <c r="C8" t="n">
-        <v>838</v>
+        <v>493</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C9" t="n">
-        <v>386</v>
+        <v>269</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5325</v>
+        <v>9730</v>
       </c>
       <c r="C2" t="n">
-        <v>7588</v>
+        <v>7525</v>
       </c>
       <c r="D2" t="n">
-        <v>31553</v>
+        <v>23431</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3078</v>
+        <v>5511</v>
       </c>
       <c r="C3" t="n">
-        <v>7401</v>
+        <v>4824</v>
       </c>
       <c r="D3" t="n">
-        <v>18784</v>
+        <v>13135</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2092</v>
+        <v>3632</v>
       </c>
       <c r="C4" t="n">
-        <v>5639</v>
+        <v>5724</v>
       </c>
       <c r="D4" t="n">
-        <v>9838</v>
+        <v>6245</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1591</v>
+        <v>2486</v>
       </c>
       <c r="C5" t="n">
-        <v>5297</v>
+        <v>5401</v>
       </c>
       <c r="D5" t="n">
-        <v>3907</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1012</v>
+        <v>1554</v>
       </c>
       <c r="C6" t="n">
-        <v>3889</v>
+        <v>3264</v>
       </c>
       <c r="D6" t="n">
-        <v>1540</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>523</v>
+        <v>817</v>
       </c>
       <c r="C7" t="n">
-        <v>2364</v>
+        <v>1495</v>
       </c>
       <c r="D7" t="n">
-        <v>741</v>
+        <v>671</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>223</v>
+        <v>359</v>
       </c>
       <c r="C8" t="n">
-        <v>1190</v>
+        <v>739</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="C9" t="n">
-        <v>571</v>
+        <v>362</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>282</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6673</v>
+        <v>10804</v>
       </c>
       <c r="C2" t="n">
-        <v>11333</v>
+        <v>9434</v>
       </c>
       <c r="D2" t="n">
-        <v>27073</v>
+        <v>22832</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3228</v>
+        <v>5930</v>
       </c>
       <c r="C3" t="n">
-        <v>6639</v>
+        <v>5297</v>
       </c>
       <c r="D3" t="n">
-        <v>19114</v>
+        <v>13591</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2111</v>
+        <v>3796</v>
       </c>
       <c r="C4" t="n">
-        <v>6282</v>
+        <v>5190</v>
       </c>
       <c r="D4" t="n">
-        <v>10732</v>
+        <v>7053</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1597</v>
+        <v>2623</v>
       </c>
       <c r="C5" t="n">
-        <v>5277</v>
+        <v>5379</v>
       </c>
       <c r="D5" t="n">
-        <v>4642</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1131</v>
+        <v>1768</v>
       </c>
       <c r="C6" t="n">
-        <v>4384</v>
+        <v>4156</v>
       </c>
       <c r="D6" t="n">
-        <v>1823</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>641</v>
+        <v>1007</v>
       </c>
       <c r="C7" t="n">
-        <v>2975</v>
+        <v>2225</v>
       </c>
       <c r="D7" t="n">
-        <v>843</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>301</v>
+        <v>486</v>
       </c>
       <c r="C8" t="n">
-        <v>1626</v>
+        <v>1049</v>
       </c>
       <c r="D8" t="n">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>119</v>
+        <v>191</v>
       </c>
       <c r="C9" t="n">
-        <v>795</v>
+        <v>506</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>386</v>
+        <v>280</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6059</v>
+        <v>9870</v>
       </c>
       <c r="C2" t="n">
-        <v>7797</v>
+        <v>6264</v>
       </c>
       <c r="D2" t="n">
-        <v>22575</v>
+        <v>18604</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3833</v>
+        <v>7073</v>
       </c>
       <c r="C3" t="n">
-        <v>10235</v>
+        <v>8410</v>
       </c>
       <c r="D3" t="n">
-        <v>20728</v>
+        <v>14807</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1475</v>
+        <v>2423</v>
       </c>
       <c r="C4" t="n">
-        <v>8503</v>
+        <v>8103</v>
       </c>
       <c r="D4" t="n">
-        <v>10214</v>
+        <v>6677</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1045</v>
+        <v>1633</v>
       </c>
       <c r="C5" t="n">
-        <v>4296</v>
+        <v>4072</v>
       </c>
       <c r="D5" t="n">
-        <v>3034</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>592</v>
+        <v>930</v>
       </c>
       <c r="C6" t="n">
-        <v>2915</v>
+        <v>2180</v>
       </c>
       <c r="D6" t="n">
-        <v>826</v>
+        <v>714</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>278</v>
+        <v>449</v>
       </c>
       <c r="C7" t="n">
-        <v>1593</v>
+        <v>1028</v>
       </c>
       <c r="D7" t="n">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>176</v>
       </c>
       <c r="C8" t="n">
-        <v>779</v>
+        <v>495</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>378</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3571</v>
+        <v>5939</v>
       </c>
       <c r="C2" t="n">
-        <v>3561</v>
+        <v>3305</v>
       </c>
       <c r="D2" t="n">
-        <v>16358</v>
+        <v>13796</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4094</v>
+        <v>7173</v>
       </c>
       <c r="C3" t="n">
-        <v>8290</v>
+        <v>6692</v>
       </c>
       <c r="D3" t="n">
-        <v>19984</v>
+        <v>14619</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2065</v>
+        <v>3676</v>
       </c>
       <c r="C4" t="n">
-        <v>9450</v>
+        <v>8315</v>
       </c>
       <c r="D4" t="n">
-        <v>11515</v>
+        <v>7786</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1141</v>
+        <v>1839</v>
       </c>
       <c r="C5" t="n">
-        <v>6109</v>
+        <v>5924</v>
       </c>
       <c r="D5" t="n">
-        <v>3896</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>703</v>
+        <v>1127</v>
       </c>
       <c r="C6" t="n">
-        <v>3528</v>
+        <v>3002</v>
       </c>
       <c r="D6" t="n">
-        <v>1052</v>
+        <v>856</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>260</v>
+        <v>425</v>
       </c>
       <c r="C7" t="n">
-        <v>2082</v>
+        <v>1435</v>
       </c>
       <c r="D7" t="n">
-        <v>527</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="C8" t="n">
-        <v>1019</v>
+        <v>668</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>423</v>
+        <v>328</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2136,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
         <v>211</v>
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3069</v>
+        <v>6053</v>
       </c>
       <c r="C2" t="n">
-        <v>5221</v>
+        <v>11979</v>
       </c>
       <c r="D2" t="n">
-        <v>18655</v>
+        <v>17685</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3257</v>
+        <v>5574</v>
       </c>
       <c r="C3" t="n">
-        <v>5432</v>
+        <v>4447</v>
       </c>
       <c r="D3" t="n">
-        <v>18147</v>
+        <v>13494</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2520</v>
+        <v>4507</v>
       </c>
       <c r="C4" t="n">
-        <v>8696</v>
+        <v>7316</v>
       </c>
       <c r="D4" t="n">
-        <v>12547</v>
+        <v>8730</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1353</v>
+        <v>2323</v>
       </c>
       <c r="C5" t="n">
-        <v>7521</v>
+        <v>7028</v>
       </c>
       <c r="D5" t="n">
-        <v>4947</v>
+        <v>3437</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>810</v>
+        <v>1316</v>
       </c>
       <c r="C6" t="n">
-        <v>4668</v>
+        <v>4318</v>
       </c>
       <c r="D6" t="n">
-        <v>1447</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>380</v>
+        <v>628</v>
       </c>
       <c r="C7" t="n">
-        <v>2690</v>
+        <v>2154</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>217</v>
       </c>
       <c r="C8" t="n">
-        <v>1455</v>
+        <v>997</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>653</v>
+        <v>464</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>294</v>
+        <v>263</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1835</v>
+        <v>3600</v>
       </c>
       <c r="C2" t="n">
-        <v>2493</v>
+        <v>5399</v>
       </c>
       <c r="D2" t="n">
-        <v>13044</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3101</v>
+        <v>5489</v>
       </c>
       <c r="C3" t="n">
-        <v>5206</v>
+        <v>6948</v>
       </c>
       <c r="D3" t="n">
-        <v>17793</v>
+        <v>13639</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2770</v>
+        <v>4960</v>
       </c>
       <c r="C4" t="n">
-        <v>8315</v>
+        <v>6874</v>
       </c>
       <c r="D4" t="n">
-        <v>13299</v>
+        <v>9340</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1414</v>
+        <v>2407</v>
       </c>
       <c r="C5" t="n">
-        <v>8886</v>
+        <v>8129</v>
       </c>
       <c r="D5" t="n">
-        <v>5218</v>
+        <v>3745</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>672</v>
+        <v>1127</v>
       </c>
       <c r="C6" t="n">
-        <v>5531</v>
+        <v>5189</v>
       </c>
       <c r="D6" t="n">
-        <v>1407</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>122</v>
+        <v>200</v>
       </c>
       <c r="C7" t="n">
-        <v>2750</v>
+        <v>2111</v>
       </c>
       <c r="D7" t="n">
-        <v>588</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>1081</v>
+        <v>777</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>288</v>
+        <v>257</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2395</v>
+        <v>4918</v>
       </c>
       <c r="C2" t="n">
-        <v>5675</v>
+        <v>6686</v>
       </c>
       <c r="D2" t="n">
-        <v>20950</v>
+        <v>14554</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2225</v>
+        <v>4015</v>
       </c>
       <c r="C3" t="n">
-        <v>3576</v>
+        <v>5514</v>
       </c>
       <c r="D3" t="n">
-        <v>16122</v>
+        <v>12526</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2538</v>
+        <v>4532</v>
       </c>
       <c r="C4" t="n">
-        <v>6709</v>
+        <v>6833</v>
       </c>
       <c r="D4" t="n">
-        <v>13584</v>
+        <v>9757</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1727</v>
+        <v>3053</v>
       </c>
       <c r="C5" t="n">
-        <v>8534</v>
+        <v>7459</v>
       </c>
       <c r="D5" t="n">
-        <v>6223</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>864</v>
+        <v>1483</v>
       </c>
       <c r="C6" t="n">
-        <v>6920</v>
+        <v>6461</v>
       </c>
       <c r="D6" t="n">
-        <v>1900</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>250</v>
+        <v>435</v>
       </c>
       <c r="C7" t="n">
-        <v>3892</v>
+        <v>3418</v>
       </c>
       <c r="D7" t="n">
-        <v>692</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>1690</v>
+        <v>1288</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>545</v>
+        <v>437</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1620</v>
+        <v>3700</v>
       </c>
       <c r="C2" t="n">
-        <v>3238</v>
+        <v>4642</v>
       </c>
       <c r="D2" t="n">
-        <v>14706</v>
+        <v>10720</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1997</v>
+        <v>3776</v>
       </c>
       <c r="C3" t="n">
-        <v>4023</v>
+        <v>5477</v>
       </c>
       <c r="D3" t="n">
-        <v>15979</v>
+        <v>12087</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2236</v>
+        <v>4033</v>
       </c>
       <c r="C4" t="n">
-        <v>5465</v>
+        <v>6277</v>
       </c>
       <c r="D4" t="n">
-        <v>13618</v>
+        <v>9926</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1879</v>
+        <v>3314</v>
       </c>
       <c r="C5" t="n">
-        <v>8035</v>
+        <v>7355</v>
       </c>
       <c r="D5" t="n">
-        <v>6870</v>
+        <v>5046</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1010</v>
+        <v>1779</v>
       </c>
       <c r="C6" t="n">
-        <v>7693</v>
+        <v>7048</v>
       </c>
       <c r="D6" t="n">
-        <v>2306</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>225</v>
+        <v>409</v>
       </c>
       <c r="C7" t="n">
-        <v>4869</v>
+        <v>4426</v>
       </c>
       <c r="D7" t="n">
-        <v>776</v>
+        <v>699</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>2188</v>
+        <v>1773</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>623</v>
+        <v>530</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2696</v>
+        <v>5845</v>
       </c>
       <c r="C2" t="n">
-        <v>6723</v>
+        <v>12285</v>
       </c>
       <c r="D2" t="n">
-        <v>15776</v>
+        <v>12364</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1572</v>
+        <v>3154</v>
       </c>
       <c r="C3" t="n">
-        <v>3341</v>
+        <v>4562</v>
       </c>
       <c r="D3" t="n">
-        <v>14803</v>
+        <v>11149</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1871</v>
+        <v>3426</v>
       </c>
       <c r="C4" t="n">
-        <v>4756</v>
+        <v>5800</v>
       </c>
       <c r="D4" t="n">
-        <v>13543</v>
+        <v>9935</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1844</v>
+        <v>3250</v>
       </c>
       <c r="C5" t="n">
-        <v>6856</v>
+        <v>6757</v>
       </c>
       <c r="D5" t="n">
-        <v>7568</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1202</v>
+        <v>2146</v>
       </c>
       <c r="C6" t="n">
-        <v>7757</v>
+        <v>7108</v>
       </c>
       <c r="D6" t="n">
-        <v>2846</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>409</v>
+        <v>756</v>
       </c>
       <c r="C7" t="n">
-        <v>5891</v>
+        <v>5426</v>
       </c>
       <c r="D7" t="n">
-        <v>948</v>
+        <v>827</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="C8" t="n">
-        <v>3128</v>
+        <v>2751</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>1113</v>
+        <v>949</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4472</v>
+        <v>7492</v>
       </c>
       <c r="C2" t="n">
-        <v>8296</v>
+        <v>3007</v>
       </c>
       <c r="D2" t="n">
-        <v>9456</v>
+        <v>6152</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1947</v>
+        <v>4185</v>
       </c>
       <c r="C2" t="n">
-        <v>3872</v>
+        <v>6977</v>
       </c>
       <c r="D2" t="n">
-        <v>11737</v>
+        <v>9099</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2160</v>
+        <v>4281</v>
       </c>
       <c r="C3" t="n">
-        <v>4392</v>
+        <v>6747</v>
       </c>
       <c r="D3" t="n">
-        <v>16004</v>
+        <v>12161</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2658</v>
+        <v>4751</v>
       </c>
       <c r="C4" t="n">
-        <v>7058</v>
+        <v>8125</v>
       </c>
       <c r="D4" t="n">
-        <v>13907</v>
+        <v>10137</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1144</v>
+        <v>2072</v>
       </c>
       <c r="C5" t="n">
-        <v>10567</v>
+        <v>9983</v>
       </c>
       <c r="D5" t="n">
-        <v>6843</v>
+        <v>5082</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>377</v>
+        <v>698</v>
       </c>
       <c r="C6" t="n">
-        <v>7217</v>
+        <v>6710</v>
       </c>
       <c r="D6" t="n">
-        <v>2202</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>3065</v>
+        <v>2695</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1090</v>
+        <v>930</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5513</v>
+        <v>8205</v>
       </c>
       <c r="C2" t="n">
-        <v>4041</v>
+        <v>1978</v>
       </c>
       <c r="D2" t="n">
-        <v>20746</v>
+        <v>6428</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1901</v>
+        <v>3182</v>
       </c>
       <c r="C3" t="n">
-        <v>4181</v>
+        <v>1539</v>
       </c>
       <c r="D3" t="n">
-        <v>2227</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4557,7 +4557,7 @@
         <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3942</v>
+        <v>5002</v>
       </c>
       <c r="C2" t="n">
-        <v>5494</v>
+        <v>5165</v>
       </c>
       <c r="D2" t="n">
-        <v>33698</v>
+        <v>9380</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3042</v>
+        <v>4741</v>
       </c>
       <c r="C3" t="n">
-        <v>3537</v>
+        <v>1542</v>
       </c>
       <c r="D3" t="n">
-        <v>5174</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>860</v>
+        <v>1416</v>
       </c>
       <c r="C4" t="n">
-        <v>2494</v>
+        <v>959</v>
       </c>
       <c r="D4" t="n">
-        <v>1630</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4907,10 +4907,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
         <v>441</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5008,7 +5008,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4303</v>
+        <v>5520</v>
       </c>
       <c r="C2" t="n">
-        <v>6744</v>
+        <v>3981</v>
       </c>
       <c r="D2" t="n">
-        <v>25247</v>
+        <v>12187</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2867</v>
+        <v>4020</v>
       </c>
       <c r="C3" t="n">
-        <v>3985</v>
+        <v>3071</v>
       </c>
       <c r="D3" t="n">
-        <v>9365</v>
+        <v>3332</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1658</v>
+        <v>2647</v>
       </c>
       <c r="C4" t="n">
-        <v>3032</v>
+        <v>1274</v>
       </c>
       <c r="D4" t="n">
-        <v>2260</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>406</v>
+        <v>640</v>
       </c>
       <c r="C5" t="n">
-        <v>1459</v>
+        <v>626</v>
       </c>
       <c r="D5" t="n">
-        <v>1228</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11">
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
         <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5082</v>
+        <v>6738</v>
       </c>
       <c r="C2" t="n">
-        <v>12643</v>
+        <v>7495</v>
       </c>
       <c r="D2" t="n">
-        <v>29074</v>
+        <v>23636</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2912</v>
+        <v>3900</v>
       </c>
       <c r="C3" t="n">
-        <v>4704</v>
+        <v>3114</v>
       </c>
       <c r="D3" t="n">
-        <v>11119</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1925</v>
+        <v>2861</v>
       </c>
       <c r="C4" t="n">
-        <v>3481</v>
+        <v>2218</v>
       </c>
       <c r="D4" t="n">
-        <v>3487</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>845</v>
+        <v>1362</v>
       </c>
       <c r="C5" t="n">
-        <v>2230</v>
+        <v>961</v>
       </c>
       <c r="D5" t="n">
-        <v>1357</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>244</v>
+        <v>343</v>
       </c>
       <c r="C6" t="n">
-        <v>888</v>
+        <v>467</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>941</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4779</v>
+        <v>7583</v>
       </c>
       <c r="C2" t="n">
-        <v>7160</v>
+        <v>13720</v>
       </c>
       <c r="D2" t="n">
-        <v>31273</v>
+        <v>25035</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2878</v>
+        <v>3883</v>
       </c>
       <c r="C3" t="n">
-        <v>7176</v>
+        <v>4450</v>
       </c>
       <c r="D3" t="n">
-        <v>12292</v>
+        <v>6847</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1491</v>
+        <v>2124</v>
       </c>
       <c r="C4" t="n">
-        <v>3403</v>
+        <v>2241</v>
       </c>
       <c r="D4" t="n">
-        <v>4165</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>725</v>
+        <v>1113</v>
       </c>
       <c r="C5" t="n">
-        <v>2086</v>
+        <v>1193</v>
       </c>
       <c r="D5" t="n">
-        <v>1353</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>256</v>
+        <v>411</v>
       </c>
       <c r="C6" t="n">
-        <v>1054</v>
+        <v>489</v>
       </c>
       <c r="D6" t="n">
-        <v>773</v>
+        <v>749</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C7" t="n">
-        <v>391</v>
+        <v>262</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3905</v>
+        <v>7762</v>
       </c>
       <c r="C2" t="n">
-        <v>8451</v>
+        <v>7037</v>
       </c>
       <c r="D2" t="n">
-        <v>33650</v>
+        <v>22347</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3178</v>
+        <v>4825</v>
       </c>
       <c r="C3" t="n">
-        <v>6157</v>
+        <v>8739</v>
       </c>
       <c r="D3" t="n">
-        <v>14576</v>
+        <v>9533</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1922</v>
+        <v>2670</v>
       </c>
       <c r="C4" t="n">
-        <v>5614</v>
+        <v>3551</v>
       </c>
       <c r="D4" t="n">
-        <v>5636</v>
+        <v>2988</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>989</v>
+        <v>1463</v>
       </c>
       <c r="C5" t="n">
-        <v>2813</v>
+        <v>1812</v>
       </c>
       <c r="D5" t="n">
-        <v>1878</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>451</v>
+        <v>714</v>
       </c>
       <c r="C6" t="n">
-        <v>1625</v>
+        <v>901</v>
       </c>
       <c r="D6" t="n">
-        <v>873</v>
+        <v>804</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>155</v>
+        <v>240</v>
       </c>
       <c r="C7" t="n">
-        <v>757</v>
+        <v>395</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>315</v>
+        <v>243</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
         <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3986</v>
+        <v>7334</v>
       </c>
       <c r="C2" t="n">
-        <v>6396</v>
+        <v>5410</v>
       </c>
       <c r="D2" t="n">
-        <v>35787</v>
+        <v>21379</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2911</v>
+        <v>5181</v>
       </c>
       <c r="C3" t="n">
-        <v>6471</v>
+        <v>6705</v>
       </c>
       <c r="D3" t="n">
-        <v>16578</v>
+        <v>10984</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2194</v>
+        <v>3256</v>
       </c>
       <c r="C4" t="n">
-        <v>5745</v>
+        <v>6515</v>
       </c>
       <c r="D4" t="n">
-        <v>7181</v>
+        <v>4216</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1263</v>
+        <v>1817</v>
       </c>
       <c r="C5" t="n">
-        <v>4287</v>
+        <v>2741</v>
       </c>
       <c r="D5" t="n">
-        <v>2488</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>653</v>
+        <v>1005</v>
       </c>
       <c r="C6" t="n">
-        <v>2233</v>
+        <v>1397</v>
       </c>
       <c r="D6" t="n">
-        <v>1044</v>
+        <v>861</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>264</v>
+        <v>425</v>
       </c>
       <c r="C7" t="n">
-        <v>1200</v>
+        <v>672</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="C8" t="n">
-        <v>540</v>
+        <v>323</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>261</v>
+        <v>227</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_9_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_9_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8825</v>
+        <v>4792</v>
       </c>
       <c r="C2" t="n">
-        <v>5800</v>
+        <v>7612</v>
       </c>
       <c r="D2" t="n">
-        <v>26768</v>
+        <v>27594</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5097</v>
+        <v>3455</v>
       </c>
       <c r="C3" t="n">
-        <v>5234</v>
+        <v>7246</v>
       </c>
       <c r="D3" t="n">
-        <v>11790</v>
+        <v>17973</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3572</v>
+        <v>2887</v>
       </c>
       <c r="C4" t="n">
-        <v>6483</v>
+        <v>4505</v>
       </c>
       <c r="D4" t="n">
-        <v>5281</v>
+        <v>9607</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2216</v>
+        <v>1807</v>
       </c>
       <c r="C5" t="n">
-        <v>4676</v>
+        <v>3925</v>
       </c>
       <c r="D5" t="n">
-        <v>1971</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1268</v>
+        <v>960</v>
       </c>
       <c r="C6" t="n">
-        <v>2051</v>
+        <v>2747</v>
       </c>
       <c r="D6" t="n">
-        <v>964</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>630</v>
+        <v>429</v>
       </c>
       <c r="C7" t="n">
-        <v>1041</v>
+        <v>1761</v>
       </c>
       <c r="D7" t="n">
-        <v>632</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>238</v>
+        <v>158</v>
       </c>
       <c r="C8" t="n">
-        <v>493</v>
+        <v>824</v>
       </c>
       <c r="D8" t="n">
         <v>433</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>269</v>
+        <v>357</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
         <v>202</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9730</v>
+        <v>6442</v>
       </c>
       <c r="C2" t="n">
-        <v>7525</v>
+        <v>6421</v>
       </c>
       <c r="D2" t="n">
-        <v>23431</v>
+        <v>29721</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5511</v>
+        <v>3308</v>
       </c>
       <c r="C3" t="n">
-        <v>4824</v>
+        <v>6531</v>
       </c>
       <c r="D3" t="n">
-        <v>13135</v>
+        <v>18073</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3632</v>
+        <v>2682</v>
       </c>
       <c r="C4" t="n">
-        <v>5724</v>
+        <v>5657</v>
       </c>
       <c r="D4" t="n">
-        <v>6245</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2486</v>
+        <v>2019</v>
       </c>
       <c r="C5" t="n">
-        <v>5401</v>
+        <v>4110</v>
       </c>
       <c r="D5" t="n">
-        <v>2432</v>
+        <v>4413</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1554</v>
+        <v>1193</v>
       </c>
       <c r="C6" t="n">
-        <v>3264</v>
+        <v>3213</v>
       </c>
       <c r="D6" t="n">
-        <v>1115</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>817</v>
+        <v>581</v>
       </c>
       <c r="C7" t="n">
-        <v>1495</v>
+        <v>2195</v>
       </c>
       <c r="D7" t="n">
-        <v>671</v>
+        <v>774</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>359</v>
+        <v>237</v>
       </c>
       <c r="C8" t="n">
-        <v>739</v>
+        <v>1210</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>362</v>
+        <v>549</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
         <v>165</v>
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10804</v>
+        <v>7071</v>
       </c>
       <c r="C2" t="n">
-        <v>9434</v>
+        <v>9608</v>
       </c>
       <c r="D2" t="n">
-        <v>22832</v>
+        <v>24301</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5930</v>
+        <v>3733</v>
       </c>
       <c r="C3" t="n">
-        <v>5297</v>
+        <v>5759</v>
       </c>
       <c r="D3" t="n">
-        <v>13591</v>
+        <v>18314</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3796</v>
+        <v>2505</v>
       </c>
       <c r="C4" t="n">
-        <v>5190</v>
+        <v>5862</v>
       </c>
       <c r="D4" t="n">
-        <v>7053</v>
+        <v>11317</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2623</v>
+        <v>2035</v>
       </c>
       <c r="C5" t="n">
-        <v>5379</v>
+        <v>4677</v>
       </c>
       <c r="D5" t="n">
-        <v>2943</v>
+        <v>5181</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1768</v>
+        <v>1380</v>
       </c>
       <c r="C6" t="n">
-        <v>4156</v>
+        <v>3514</v>
       </c>
       <c r="D6" t="n">
-        <v>1279</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1007</v>
+        <v>734</v>
       </c>
       <c r="C7" t="n">
-        <v>2225</v>
+        <v>2581</v>
       </c>
       <c r="D7" t="n">
-        <v>729</v>
+        <v>892</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>486</v>
+        <v>328</v>
       </c>
       <c r="C8" t="n">
-        <v>1049</v>
+        <v>1595</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>191</v>
+        <v>126</v>
       </c>
       <c r="C9" t="n">
-        <v>506</v>
+        <v>789</v>
       </c>
       <c r="D9" t="n">
-        <v>339</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>280</v>
+        <v>365</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9870</v>
+        <v>6491</v>
       </c>
       <c r="C2" t="n">
-        <v>6264</v>
+        <v>6533</v>
       </c>
       <c r="D2" t="n">
-        <v>18604</v>
+        <v>20319</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7073</v>
+        <v>4487</v>
       </c>
       <c r="C3" t="n">
-        <v>8410</v>
+        <v>9101</v>
       </c>
       <c r="D3" t="n">
-        <v>14807</v>
+        <v>20178</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2423</v>
+        <v>1880</v>
       </c>
       <c r="C4" t="n">
-        <v>8103</v>
+        <v>7697</v>
       </c>
       <c r="D4" t="n">
-        <v>6677</v>
+        <v>10968</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1633</v>
+        <v>1275</v>
       </c>
       <c r="C5" t="n">
-        <v>4072</v>
+        <v>3443</v>
       </c>
       <c r="D5" t="n">
-        <v>2072</v>
+        <v>3371</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>930</v>
+        <v>678</v>
       </c>
       <c r="C6" t="n">
-        <v>2180</v>
+        <v>2529</v>
       </c>
       <c r="D6" t="n">
-        <v>714</v>
+        <v>874</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>449</v>
+        <v>303</v>
       </c>
       <c r="C7" t="n">
-        <v>1028</v>
+        <v>1563</v>
       </c>
       <c r="D7" t="n">
-        <v>468</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>176</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>495</v>
+        <v>773</v>
       </c>
       <c r="D8" t="n">
-        <v>332</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>274</v>
+        <v>357</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5939</v>
+        <v>3870</v>
       </c>
       <c r="C2" t="n">
-        <v>3305</v>
+        <v>3194</v>
       </c>
       <c r="D2" t="n">
-        <v>13796</v>
+        <v>14824</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7173</v>
+        <v>4600</v>
       </c>
       <c r="C3" t="n">
-        <v>6692</v>
+        <v>7208</v>
       </c>
       <c r="D3" t="n">
-        <v>14619</v>
+        <v>19228</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3676</v>
+        <v>2501</v>
       </c>
       <c r="C4" t="n">
-        <v>8315</v>
+        <v>8405</v>
       </c>
       <c r="D4" t="n">
-        <v>7786</v>
+        <v>12066</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1839</v>
+        <v>1425</v>
       </c>
       <c r="C5" t="n">
-        <v>5924</v>
+        <v>5292</v>
       </c>
       <c r="D5" t="n">
-        <v>2687</v>
+        <v>4281</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1127</v>
+        <v>810</v>
       </c>
       <c r="C6" t="n">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="D6" t="n">
-        <v>856</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>425</v>
+        <v>285</v>
       </c>
       <c r="C7" t="n">
-        <v>1435</v>
+        <v>1940</v>
       </c>
       <c r="D7" t="n">
-        <v>505</v>
+        <v>534</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>668</v>
+        <v>1023</v>
       </c>
       <c r="D8" t="n">
-        <v>347</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6053</v>
+        <v>4758</v>
       </c>
       <c r="C2" t="n">
-        <v>11979</v>
+        <v>8173</v>
       </c>
       <c r="D2" t="n">
-        <v>17685</v>
+        <v>24435</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5574</v>
+        <v>3643</v>
       </c>
       <c r="C3" t="n">
-        <v>4447</v>
+        <v>4719</v>
       </c>
       <c r="D3" t="n">
-        <v>13494</v>
+        <v>17336</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4507</v>
+        <v>2906</v>
       </c>
       <c r="C4" t="n">
-        <v>7316</v>
+        <v>7644</v>
       </c>
       <c r="D4" t="n">
-        <v>8730</v>
+        <v>12868</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2323</v>
+        <v>1673</v>
       </c>
       <c r="C5" t="n">
-        <v>7028</v>
+        <v>6697</v>
       </c>
       <c r="D5" t="n">
-        <v>3437</v>
+        <v>5346</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1316</v>
+        <v>982</v>
       </c>
       <c r="C6" t="n">
-        <v>4318</v>
+        <v>3982</v>
       </c>
       <c r="D6" t="n">
-        <v>1125</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>628</v>
+        <v>426</v>
       </c>
       <c r="C7" t="n">
-        <v>2154</v>
+        <v>2414</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>217</v>
+        <v>145</v>
       </c>
       <c r="C8" t="n">
-        <v>997</v>
+        <v>1401</v>
       </c>
       <c r="D8" t="n">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>464</v>
+        <v>635</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
         <v>170</v>
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3600</v>
+        <v>2804</v>
       </c>
       <c r="C2" t="n">
-        <v>5399</v>
+        <v>3853</v>
       </c>
       <c r="D2" t="n">
-        <v>12200</v>
+        <v>17050</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5489</v>
+        <v>3804</v>
       </c>
       <c r="C3" t="n">
-        <v>6948</v>
+        <v>5736</v>
       </c>
       <c r="D3" t="n">
-        <v>13639</v>
+        <v>17685</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4960</v>
+        <v>3188</v>
       </c>
       <c r="C4" t="n">
-        <v>6874</v>
+        <v>7264</v>
       </c>
       <c r="D4" t="n">
-        <v>9340</v>
+        <v>13531</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2407</v>
+        <v>1744</v>
       </c>
       <c r="C5" t="n">
-        <v>8129</v>
+        <v>7956</v>
       </c>
       <c r="D5" t="n">
-        <v>3745</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1127</v>
+        <v>792</v>
       </c>
       <c r="C6" t="n">
-        <v>5189</v>
+        <v>4770</v>
       </c>
       <c r="D6" t="n">
-        <v>1121</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="C7" t="n">
-        <v>2111</v>
+        <v>2532</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>777</v>
+        <v>1047</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4918</v>
+        <v>2720</v>
       </c>
       <c r="C2" t="n">
-        <v>6686</v>
+        <v>8793</v>
       </c>
       <c r="D2" t="n">
-        <v>14554</v>
+        <v>22947</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4015</v>
+        <v>2896</v>
       </c>
       <c r="C3" t="n">
-        <v>5514</v>
+        <v>4349</v>
       </c>
       <c r="D3" t="n">
-        <v>12526</v>
+        <v>16579</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4532</v>
+        <v>3029</v>
       </c>
       <c r="C4" t="n">
-        <v>6833</v>
+        <v>6463</v>
       </c>
       <c r="D4" t="n">
-        <v>9757</v>
+        <v>13757</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3053</v>
+        <v>2062</v>
       </c>
       <c r="C5" t="n">
-        <v>7459</v>
+        <v>7561</v>
       </c>
       <c r="D5" t="n">
-        <v>4490</v>
+        <v>6588</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1483</v>
+        <v>1033</v>
       </c>
       <c r="C6" t="n">
-        <v>6461</v>
+        <v>6088</v>
       </c>
       <c r="D6" t="n">
-        <v>1495</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>435</v>
+        <v>294</v>
       </c>
       <c r="C7" t="n">
-        <v>3418</v>
+        <v>3433</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>1288</v>
+        <v>1615</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>437</v>
+        <v>526</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3700</v>
+        <v>1857</v>
       </c>
       <c r="C2" t="n">
-        <v>4642</v>
+        <v>5360</v>
       </c>
       <c r="D2" t="n">
-        <v>10720</v>
+        <v>16750</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3776</v>
+        <v>2488</v>
       </c>
       <c r="C3" t="n">
-        <v>5477</v>
+        <v>5516</v>
       </c>
       <c r="D3" t="n">
-        <v>12087</v>
+        <v>16441</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4033</v>
+        <v>2753</v>
       </c>
       <c r="C4" t="n">
-        <v>6277</v>
+        <v>5662</v>
       </c>
       <c r="D4" t="n">
-        <v>9926</v>
+        <v>13982</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3314</v>
+        <v>2244</v>
       </c>
       <c r="C5" t="n">
-        <v>7355</v>
+        <v>7304</v>
       </c>
       <c r="D5" t="n">
-        <v>5046</v>
+        <v>7208</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1779</v>
+        <v>1204</v>
       </c>
       <c r="C6" t="n">
-        <v>7048</v>
+        <v>6784</v>
       </c>
       <c r="D6" t="n">
-        <v>1765</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>409</v>
+        <v>265</v>
       </c>
       <c r="C7" t="n">
-        <v>4426</v>
+        <v>4257</v>
       </c>
       <c r="D7" t="n">
-        <v>699</v>
+        <v>809</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1773</v>
+        <v>2083</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>530</v>
+        <v>599</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5845</v>
+        <v>2785</v>
       </c>
       <c r="C2" t="n">
-        <v>12285</v>
+        <v>10556</v>
       </c>
       <c r="D2" t="n">
-        <v>12364</v>
+        <v>15585</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3154</v>
+        <v>1912</v>
       </c>
       <c r="C3" t="n">
-        <v>4562</v>
+        <v>4852</v>
       </c>
       <c r="D3" t="n">
-        <v>11149</v>
+        <v>15425</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3426</v>
+        <v>2313</v>
       </c>
       <c r="C4" t="n">
-        <v>5800</v>
+        <v>5482</v>
       </c>
       <c r="D4" t="n">
-        <v>9935</v>
+        <v>13911</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3250</v>
+        <v>2204</v>
       </c>
       <c r="C5" t="n">
-        <v>6757</v>
+        <v>6490</v>
       </c>
       <c r="D5" t="n">
-        <v>5500</v>
+        <v>7899</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2146</v>
+        <v>1443</v>
       </c>
       <c r="C6" t="n">
-        <v>7108</v>
+        <v>6926</v>
       </c>
       <c r="D6" t="n">
-        <v>2183</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>756</v>
+        <v>495</v>
       </c>
       <c r="C7" t="n">
-        <v>5426</v>
+        <v>5238</v>
       </c>
       <c r="D7" t="n">
-        <v>827</v>
+        <v>996</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>2751</v>
+        <v>2827</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>949</v>
+        <v>1084</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="D10" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7492</v>
+        <v>4600</v>
       </c>
       <c r="C2" t="n">
-        <v>3007</v>
+        <v>6110</v>
       </c>
       <c r="D2" t="n">
-        <v>6152</v>
+        <v>12778</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4185</v>
+        <v>2016</v>
       </c>
       <c r="C2" t="n">
-        <v>6977</v>
+        <v>6080</v>
       </c>
       <c r="D2" t="n">
-        <v>9099</v>
+        <v>11595</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4281</v>
+        <v>2600</v>
       </c>
       <c r="C3" t="n">
-        <v>6747</v>
+        <v>6556</v>
       </c>
       <c r="D3" t="n">
-        <v>12161</v>
+        <v>16615</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4751</v>
+        <v>3217</v>
       </c>
       <c r="C4" t="n">
-        <v>8125</v>
+        <v>7784</v>
       </c>
       <c r="D4" t="n">
-        <v>10137</v>
+        <v>14315</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2072</v>
+        <v>1374</v>
       </c>
       <c r="C5" t="n">
-        <v>9983</v>
+        <v>9672</v>
       </c>
       <c r="D5" t="n">
-        <v>5082</v>
+        <v>7173</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>698</v>
+        <v>457</v>
       </c>
       <c r="C6" t="n">
-        <v>6710</v>
+        <v>6422</v>
       </c>
       <c r="D6" t="n">
-        <v>1774</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>2695</v>
+        <v>2770</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>930</v>
+        <v>1062</v>
       </c>
       <c r="D8" t="n">
-        <v>303</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="D9" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8205</v>
+        <v>6397</v>
       </c>
       <c r="C2" t="n">
-        <v>1978</v>
+        <v>7936</v>
       </c>
       <c r="D2" t="n">
-        <v>6428</v>
+        <v>31595</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3182</v>
+        <v>1956</v>
       </c>
       <c r="C3" t="n">
-        <v>1539</v>
+        <v>3079</v>
       </c>
       <c r="D3" t="n">
-        <v>1722</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4557,7 +4557,7 @@
         <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4574,7 +4574,7 @@
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5002</v>
+        <v>4673</v>
       </c>
       <c r="C2" t="n">
-        <v>5165</v>
+        <v>3865</v>
       </c>
       <c r="D2" t="n">
-        <v>9380</v>
+        <v>24173</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4741</v>
+        <v>3426</v>
       </c>
       <c r="C3" t="n">
-        <v>1542</v>
+        <v>5025</v>
       </c>
       <c r="D3" t="n">
-        <v>2385</v>
+        <v>7420</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1416</v>
+        <v>884</v>
       </c>
       <c r="C4" t="n">
-        <v>959</v>
+        <v>1849</v>
       </c>
       <c r="D4" t="n">
-        <v>1528</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5520</v>
+        <v>4966</v>
       </c>
       <c r="C2" t="n">
-        <v>3981</v>
+        <v>7854</v>
       </c>
       <c r="D2" t="n">
-        <v>12187</v>
+        <v>34606</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4020</v>
+        <v>3320</v>
       </c>
       <c r="C3" t="n">
-        <v>3071</v>
+        <v>3802</v>
       </c>
       <c r="D3" t="n">
-        <v>3332</v>
+        <v>9566</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2647</v>
+        <v>1829</v>
       </c>
       <c r="C4" t="n">
-        <v>1274</v>
+        <v>3609</v>
       </c>
       <c r="D4" t="n">
-        <v>1631</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>640</v>
+        <v>415</v>
       </c>
       <c r="C5" t="n">
-        <v>626</v>
+        <v>1108</v>
       </c>
       <c r="D5" t="n">
-        <v>1215</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5260,7 +5260,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
         <v>176</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6738</v>
+        <v>6455</v>
       </c>
       <c r="C2" t="n">
-        <v>7495</v>
+        <v>4281</v>
       </c>
       <c r="D2" t="n">
-        <v>23636</v>
+        <v>31195</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3900</v>
+        <v>3354</v>
       </c>
       <c r="C3" t="n">
-        <v>3114</v>
+        <v>5124</v>
       </c>
       <c r="D3" t="n">
-        <v>4540</v>
+        <v>12698</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2861</v>
+        <v>2158</v>
       </c>
       <c r="C4" t="n">
-        <v>2218</v>
+        <v>3637</v>
       </c>
       <c r="D4" t="n">
-        <v>1876</v>
+        <v>3932</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1362</v>
+        <v>919</v>
       </c>
       <c r="C5" t="n">
-        <v>961</v>
+        <v>2381</v>
       </c>
       <c r="D5" t="n">
-        <v>1253</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>343</v>
+        <v>244</v>
       </c>
       <c r="C6" t="n">
-        <v>467</v>
+        <v>699</v>
       </c>
       <c r="D6" t="n">
-        <v>941</v>
+        <v>954</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7583</v>
+        <v>6787</v>
       </c>
       <c r="C2" t="n">
-        <v>13720</v>
+        <v>8486</v>
       </c>
       <c r="D2" t="n">
-        <v>25035</v>
+        <v>40539</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3883</v>
+        <v>3522</v>
       </c>
       <c r="C3" t="n">
-        <v>4450</v>
+        <v>3888</v>
       </c>
       <c r="D3" t="n">
-        <v>6847</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2124</v>
+        <v>1710</v>
       </c>
       <c r="C4" t="n">
-        <v>2241</v>
+        <v>3607</v>
       </c>
       <c r="D4" t="n">
-        <v>2034</v>
+        <v>4723</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1113</v>
+        <v>792</v>
       </c>
       <c r="C5" t="n">
-        <v>1193</v>
+        <v>2212</v>
       </c>
       <c r="D5" t="n">
-        <v>1077</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>411</v>
+        <v>272</v>
       </c>
       <c r="C6" t="n">
-        <v>489</v>
+        <v>1025</v>
       </c>
       <c r="D6" t="n">
-        <v>749</v>
+        <v>792</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>262</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7762</v>
+        <v>5427</v>
       </c>
       <c r="C2" t="n">
-        <v>7037</v>
+        <v>4789</v>
       </c>
       <c r="D2" t="n">
-        <v>22347</v>
+        <v>29872</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4825</v>
+        <v>4263</v>
       </c>
       <c r="C3" t="n">
-        <v>8739</v>
+        <v>5657</v>
       </c>
       <c r="D3" t="n">
-        <v>9533</v>
+        <v>17238</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2670</v>
+        <v>2288</v>
       </c>
       <c r="C4" t="n">
-        <v>3551</v>
+        <v>3701</v>
       </c>
       <c r="D4" t="n">
-        <v>2988</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1463</v>
+        <v>1101</v>
       </c>
       <c r="C5" t="n">
-        <v>1812</v>
+        <v>2982</v>
       </c>
       <c r="D5" t="n">
-        <v>1226</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>714</v>
+        <v>491</v>
       </c>
       <c r="C6" t="n">
-        <v>901</v>
+        <v>1684</v>
       </c>
       <c r="D6" t="n">
-        <v>804</v>
+        <v>913</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>240</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>395</v>
+        <v>719</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7334</v>
+        <v>4371</v>
       </c>
       <c r="C2" t="n">
-        <v>5410</v>
+        <v>12172</v>
       </c>
       <c r="D2" t="n">
-        <v>21379</v>
+        <v>26319</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5181</v>
+        <v>4016</v>
       </c>
       <c r="C3" t="n">
-        <v>6705</v>
+        <v>4502</v>
       </c>
       <c r="D3" t="n">
-        <v>10984</v>
+        <v>18018</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3256</v>
+        <v>2776</v>
       </c>
       <c r="C4" t="n">
-        <v>6515</v>
+        <v>4713</v>
       </c>
       <c r="D4" t="n">
-        <v>4216</v>
+        <v>8249</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1817</v>
+        <v>1475</v>
       </c>
       <c r="C5" t="n">
-        <v>2741</v>
+        <v>3277</v>
       </c>
       <c r="D5" t="n">
-        <v>1527</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1005</v>
+        <v>711</v>
       </c>
       <c r="C6" t="n">
-        <v>1397</v>
+        <v>2350</v>
       </c>
       <c r="D6" t="n">
-        <v>861</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>425</v>
+        <v>285</v>
       </c>
       <c r="C7" t="n">
-        <v>672</v>
+        <v>1219</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>323</v>
+        <v>497</v>
       </c>
       <c r="D8" t="n">
         <v>405</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_9_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_9_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4792</v>
+        <v>837</v>
       </c>
       <c r="C2" t="n">
-        <v>7612</v>
+        <v>3402</v>
       </c>
       <c r="D2" t="n">
-        <v>27594</v>
+        <v>9888</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3455</v>
+        <v>1682</v>
       </c>
       <c r="C3" t="n">
-        <v>7246</v>
+        <v>6728</v>
       </c>
       <c r="D3" t="n">
-        <v>17973</v>
+        <v>10191</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2887</v>
+        <v>1126</v>
       </c>
       <c r="C4" t="n">
-        <v>4505</v>
+        <v>8240</v>
       </c>
       <c r="D4" t="n">
-        <v>9607</v>
+        <v>5236</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1807</v>
+        <v>499</v>
       </c>
       <c r="C5" t="n">
-        <v>3925</v>
+        <v>6227</v>
       </c>
       <c r="D5" t="n">
-        <v>3643</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>960</v>
+        <v>224</v>
       </c>
       <c r="C6" t="n">
-        <v>2747</v>
+        <v>2866</v>
       </c>
       <c r="D6" t="n">
-        <v>1361</v>
+        <v>740</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>429</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>1761</v>
+        <v>975</v>
       </c>
       <c r="D7" t="n">
-        <v>689</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>158</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>824</v>
+        <v>371</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>357</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6442</v>
+        <v>1361</v>
       </c>
       <c r="C2" t="n">
-        <v>6421</v>
+        <v>14398</v>
       </c>
       <c r="D2" t="n">
-        <v>29721</v>
+        <v>12014</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3308</v>
+        <v>1088</v>
       </c>
       <c r="C3" t="n">
-        <v>6531</v>
+        <v>4393</v>
       </c>
       <c r="D3" t="n">
-        <v>18073</v>
+        <v>9427</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2682</v>
+        <v>1206</v>
       </c>
       <c r="C4" t="n">
-        <v>5657</v>
+        <v>7255</v>
       </c>
       <c r="D4" t="n">
-        <v>10680</v>
+        <v>5980</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2019</v>
+        <v>693</v>
       </c>
       <c r="C5" t="n">
-        <v>4110</v>
+        <v>7200</v>
       </c>
       <c r="D5" t="n">
-        <v>4413</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1193</v>
+        <v>312</v>
       </c>
       <c r="C6" t="n">
-        <v>3213</v>
+        <v>4509</v>
       </c>
       <c r="D6" t="n">
-        <v>1693</v>
+        <v>912</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>581</v>
+        <v>134</v>
       </c>
       <c r="C7" t="n">
-        <v>2195</v>
+        <v>1873</v>
       </c>
       <c r="D7" t="n">
-        <v>774</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>237</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>1210</v>
+        <v>640</v>
       </c>
       <c r="D8" t="n">
-        <v>466</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>549</v>
+        <v>321</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7071</v>
+        <v>733</v>
       </c>
       <c r="C2" t="n">
-        <v>9608</v>
+        <v>6127</v>
       </c>
       <c r="D2" t="n">
-        <v>24301</v>
+        <v>8246</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3733</v>
+        <v>1119</v>
       </c>
       <c r="C3" t="n">
-        <v>5759</v>
+        <v>7944</v>
       </c>
       <c r="D3" t="n">
-        <v>18314</v>
+        <v>9496</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2505</v>
+        <v>1296</v>
       </c>
       <c r="C4" t="n">
-        <v>5862</v>
+        <v>6771</v>
       </c>
       <c r="D4" t="n">
-        <v>11317</v>
+        <v>6449</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2035</v>
+        <v>687</v>
       </c>
       <c r="C5" t="n">
-        <v>4677</v>
+        <v>8145</v>
       </c>
       <c r="D5" t="n">
-        <v>5181</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1380</v>
+        <v>262</v>
       </c>
       <c r="C6" t="n">
-        <v>3514</v>
+        <v>5579</v>
       </c>
       <c r="D6" t="n">
-        <v>2019</v>
+        <v>930</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>734</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>2581</v>
+        <v>1729</v>
       </c>
       <c r="D7" t="n">
-        <v>892</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>328</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1595</v>
+        <v>534</v>
       </c>
       <c r="D8" t="n">
-        <v>495</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>789</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>365</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>210</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6491</v>
+        <v>1170</v>
       </c>
       <c r="C2" t="n">
-        <v>6533</v>
+        <v>12592</v>
       </c>
       <c r="D2" t="n">
-        <v>20319</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4487</v>
+        <v>807</v>
       </c>
       <c r="C3" t="n">
-        <v>9101</v>
+        <v>6203</v>
       </c>
       <c r="D3" t="n">
-        <v>20178</v>
+        <v>8662</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1880</v>
+        <v>1083</v>
       </c>
       <c r="C4" t="n">
-        <v>7697</v>
+        <v>7303</v>
       </c>
       <c r="D4" t="n">
-        <v>10968</v>
+        <v>6779</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1275</v>
+        <v>843</v>
       </c>
       <c r="C5" t="n">
-        <v>3443</v>
+        <v>7381</v>
       </c>
       <c r="D5" t="n">
-        <v>3371</v>
+        <v>3195</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>678</v>
+        <v>391</v>
       </c>
       <c r="C6" t="n">
-        <v>2529</v>
+        <v>6814</v>
       </c>
       <c r="D6" t="n">
-        <v>874</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>303</v>
+        <v>121</v>
       </c>
       <c r="C7" t="n">
-        <v>1563</v>
+        <v>3422</v>
       </c>
       <c r="D7" t="n">
-        <v>485</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>773</v>
+        <v>1012</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
         <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3870</v>
+        <v>652</v>
       </c>
       <c r="C2" t="n">
-        <v>3194</v>
+        <v>6118</v>
       </c>
       <c r="D2" t="n">
-        <v>14824</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4600</v>
+        <v>818</v>
       </c>
       <c r="C3" t="n">
-        <v>7208</v>
+        <v>8092</v>
       </c>
       <c r="D3" t="n">
-        <v>19228</v>
+        <v>8092</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2501</v>
+        <v>916</v>
       </c>
       <c r="C4" t="n">
-        <v>8405</v>
+        <v>6865</v>
       </c>
       <c r="D4" t="n">
-        <v>12066</v>
+        <v>6909</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1425</v>
+        <v>894</v>
       </c>
       <c r="C5" t="n">
-        <v>5292</v>
+        <v>7479</v>
       </c>
       <c r="D5" t="n">
-        <v>4281</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>810</v>
+        <v>477</v>
       </c>
       <c r="C6" t="n">
-        <v>2999</v>
+        <v>7358</v>
       </c>
       <c r="D6" t="n">
-        <v>1128</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>285</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>1940</v>
+        <v>4586</v>
       </c>
       <c r="D7" t="n">
-        <v>534</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1023</v>
+        <v>1556</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>400</v>
+        <v>449</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4758</v>
+        <v>995</v>
       </c>
       <c r="C2" t="n">
-        <v>8173</v>
+        <v>15529</v>
       </c>
       <c r="D2" t="n">
-        <v>24435</v>
+        <v>8435</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3643</v>
+        <v>633</v>
       </c>
       <c r="C3" t="n">
-        <v>4719</v>
+        <v>6437</v>
       </c>
       <c r="D3" t="n">
-        <v>17336</v>
+        <v>7375</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2906</v>
+        <v>763</v>
       </c>
       <c r="C4" t="n">
-        <v>7644</v>
+        <v>7287</v>
       </c>
       <c r="D4" t="n">
-        <v>12868</v>
+        <v>6880</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1673</v>
+        <v>833</v>
       </c>
       <c r="C5" t="n">
-        <v>6697</v>
+        <v>7052</v>
       </c>
       <c r="D5" t="n">
-        <v>5346</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>982</v>
+        <v>584</v>
       </c>
       <c r="C6" t="n">
-        <v>3982</v>
+        <v>7413</v>
       </c>
       <c r="D6" t="n">
-        <v>1567</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>426</v>
+        <v>224</v>
       </c>
       <c r="C7" t="n">
-        <v>2414</v>
+        <v>5697</v>
       </c>
       <c r="D7" t="n">
-        <v>610</v>
+        <v>760</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>1401</v>
+        <v>2728</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>635</v>
+        <v>843</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2804</v>
+        <v>684</v>
       </c>
       <c r="C2" t="n">
-        <v>3853</v>
+        <v>8448</v>
       </c>
       <c r="D2" t="n">
-        <v>17050</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3804</v>
+        <v>878</v>
       </c>
       <c r="C3" t="n">
-        <v>5736</v>
+        <v>9289</v>
       </c>
       <c r="D3" t="n">
-        <v>17685</v>
+        <v>8083</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3188</v>
+        <v>1153</v>
       </c>
       <c r="C4" t="n">
-        <v>7264</v>
+        <v>9823</v>
       </c>
       <c r="D4" t="n">
-        <v>13531</v>
+        <v>7115</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1744</v>
+        <v>578</v>
       </c>
       <c r="C5" t="n">
-        <v>7956</v>
+        <v>10400</v>
       </c>
       <c r="D5" t="n">
-        <v>5620</v>
+        <v>3685</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>792</v>
+        <v>206</v>
       </c>
       <c r="C6" t="n">
-        <v>4770</v>
+        <v>7253</v>
       </c>
       <c r="D6" t="n">
-        <v>1516</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>133</v>
+        <v>63</v>
       </c>
       <c r="C7" t="n">
-        <v>2532</v>
+        <v>2673</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>590</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1047</v>
+        <v>826</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2720</v>
+        <v>365</v>
       </c>
       <c r="C2" t="n">
-        <v>8793</v>
+        <v>4145</v>
       </c>
       <c r="D2" t="n">
-        <v>22947</v>
+        <v>4613</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2896</v>
+        <v>673</v>
       </c>
       <c r="C3" t="n">
-        <v>4349</v>
+        <v>7856</v>
       </c>
       <c r="D3" t="n">
-        <v>16579</v>
+        <v>7251</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3029</v>
+        <v>845</v>
       </c>
       <c r="C4" t="n">
-        <v>6463</v>
+        <v>9061</v>
       </c>
       <c r="D4" t="n">
-        <v>13757</v>
+        <v>6766</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2062</v>
+        <v>567</v>
       </c>
       <c r="C5" t="n">
-        <v>7561</v>
+        <v>8887</v>
       </c>
       <c r="D5" t="n">
-        <v>6588</v>
+        <v>3695</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1033</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>6088</v>
+        <v>7083</v>
       </c>
       <c r="D6" t="n">
-        <v>2047</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>294</v>
+        <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>3433</v>
+        <v>3284</v>
       </c>
       <c r="D7" t="n">
-        <v>719</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1615</v>
+        <v>963</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>526</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>122</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1857</v>
+        <v>451</v>
       </c>
       <c r="C2" t="n">
-        <v>5360</v>
+        <v>5801</v>
       </c>
       <c r="D2" t="n">
-        <v>16750</v>
+        <v>6639</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2488</v>
+        <v>446</v>
       </c>
       <c r="C3" t="n">
-        <v>5516</v>
+        <v>5175</v>
       </c>
       <c r="D3" t="n">
-        <v>16441</v>
+        <v>6339</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2753</v>
+        <v>674</v>
       </c>
       <c r="C4" t="n">
-        <v>5662</v>
+        <v>8224</v>
       </c>
       <c r="D4" t="n">
-        <v>13982</v>
+        <v>6648</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2244</v>
+        <v>618</v>
       </c>
       <c r="C5" t="n">
-        <v>7304</v>
+        <v>8877</v>
       </c>
       <c r="D5" t="n">
-        <v>7208</v>
+        <v>4113</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1204</v>
+        <v>329</v>
       </c>
       <c r="C6" t="n">
-        <v>6784</v>
+        <v>7891</v>
       </c>
       <c r="D6" t="n">
-        <v>2474</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>265</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>4257</v>
+        <v>5139</v>
       </c>
       <c r="D7" t="n">
-        <v>809</v>
+        <v>707</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>2083</v>
+        <v>2018</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>599</v>
+        <v>572</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2785</v>
+        <v>388</v>
       </c>
       <c r="C2" t="n">
-        <v>10556</v>
+        <v>16323</v>
       </c>
       <c r="D2" t="n">
-        <v>15585</v>
+        <v>7990</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1912</v>
+        <v>371</v>
       </c>
       <c r="C3" t="n">
-        <v>4852</v>
+        <v>4850</v>
       </c>
       <c r="D3" t="n">
-        <v>15425</v>
+        <v>5953</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2313</v>
+        <v>504</v>
       </c>
       <c r="C4" t="n">
-        <v>5482</v>
+        <v>6510</v>
       </c>
       <c r="D4" t="n">
-        <v>13911</v>
+        <v>6395</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2204</v>
+        <v>583</v>
       </c>
       <c r="C5" t="n">
-        <v>6490</v>
+        <v>8385</v>
       </c>
       <c r="D5" t="n">
-        <v>7899</v>
+        <v>4337</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1443</v>
+        <v>408</v>
       </c>
       <c r="C6" t="n">
-        <v>6926</v>
+        <v>8258</v>
       </c>
       <c r="D6" t="n">
-        <v>3033</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>495</v>
+        <v>172</v>
       </c>
       <c r="C7" t="n">
-        <v>5238</v>
+        <v>6350</v>
       </c>
       <c r="D7" t="n">
-        <v>996</v>
+        <v>861</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>2827</v>
+        <v>3332</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>1084</v>
+        <v>1147</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4600</v>
+        <v>3565</v>
       </c>
       <c r="C2" t="n">
-        <v>6110</v>
+        <v>18417</v>
       </c>
       <c r="D2" t="n">
-        <v>12778</v>
+        <v>14054</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2016</v>
+        <v>333</v>
       </c>
       <c r="C2" t="n">
-        <v>6080</v>
+        <v>13849</v>
       </c>
       <c r="D2" t="n">
-        <v>11595</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2600</v>
+        <v>313</v>
       </c>
       <c r="C3" t="n">
-        <v>6556</v>
+        <v>8437</v>
       </c>
       <c r="D3" t="n">
-        <v>16615</v>
+        <v>5816</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3217</v>
+        <v>391</v>
       </c>
       <c r="C4" t="n">
-        <v>7784</v>
+        <v>5657</v>
       </c>
       <c r="D4" t="n">
-        <v>14315</v>
+        <v>6075</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1374</v>
+        <v>504</v>
       </c>
       <c r="C5" t="n">
-        <v>9672</v>
+        <v>7356</v>
       </c>
       <c r="D5" t="n">
-        <v>7173</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="C6" t="n">
-        <v>6422</v>
+        <v>8236</v>
       </c>
       <c r="D6" t="n">
-        <v>2335</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>232</v>
       </c>
       <c r="C7" t="n">
-        <v>2770</v>
+        <v>7033</v>
       </c>
       <c r="D7" t="n">
-        <v>569</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>1062</v>
+        <v>4484</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>327</v>
+        <v>1927</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>622</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6397</v>
+        <v>3206</v>
       </c>
       <c r="C2" t="n">
-        <v>7936</v>
+        <v>11749</v>
       </c>
       <c r="D2" t="n">
-        <v>31595</v>
+        <v>18259</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1956</v>
+        <v>1151</v>
       </c>
       <c r="C3" t="n">
-        <v>3079</v>
+        <v>7273</v>
       </c>
       <c r="D3" t="n">
-        <v>2786</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4673</v>
+        <v>2124</v>
       </c>
       <c r="C2" t="n">
-        <v>3865</v>
+        <v>8950</v>
       </c>
       <c r="D2" t="n">
-        <v>24173</v>
+        <v>18374</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3426</v>
+        <v>1836</v>
       </c>
       <c r="C3" t="n">
-        <v>5025</v>
+        <v>8529</v>
       </c>
       <c r="D3" t="n">
-        <v>7420</v>
+        <v>5108</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>884</v>
+        <v>558</v>
       </c>
       <c r="C4" t="n">
-        <v>1849</v>
+        <v>4517</v>
       </c>
       <c r="D4" t="n">
-        <v>1742</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>136</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4966</v>
+        <v>2341</v>
       </c>
       <c r="C2" t="n">
-        <v>7854</v>
+        <v>4671</v>
       </c>
       <c r="D2" t="n">
-        <v>34606</v>
+        <v>16561</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3320</v>
+        <v>1633</v>
       </c>
       <c r="C3" t="n">
-        <v>3802</v>
+        <v>7560</v>
       </c>
       <c r="D3" t="n">
-        <v>9566</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1829</v>
+        <v>1040</v>
       </c>
       <c r="C4" t="n">
-        <v>3609</v>
+        <v>6772</v>
       </c>
       <c r="D4" t="n">
-        <v>2779</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>415</v>
+        <v>281</v>
       </c>
       <c r="C5" t="n">
-        <v>1108</v>
+        <v>2644</v>
       </c>
       <c r="D5" t="n">
-        <v>1249</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>264</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>328</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6455</v>
+        <v>2146</v>
       </c>
       <c r="C2" t="n">
-        <v>4281</v>
+        <v>3351</v>
       </c>
       <c r="D2" t="n">
-        <v>31195</v>
+        <v>16146</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3354</v>
+        <v>1641</v>
       </c>
       <c r="C3" t="n">
-        <v>5124</v>
+        <v>5215</v>
       </c>
       <c r="D3" t="n">
-        <v>12698</v>
+        <v>7995</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2158</v>
+        <v>1137</v>
       </c>
       <c r="C4" t="n">
-        <v>3637</v>
+        <v>7069</v>
       </c>
       <c r="D4" t="n">
-        <v>3932</v>
+        <v>3110</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>919</v>
+        <v>559</v>
       </c>
       <c r="C5" t="n">
-        <v>2381</v>
+        <v>4808</v>
       </c>
       <c r="D5" t="n">
-        <v>1463</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="C6" t="n">
-        <v>699</v>
+        <v>1492</v>
       </c>
       <c r="D6" t="n">
-        <v>954</v>
+        <v>824</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>294</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>305</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6787</v>
+        <v>2382</v>
       </c>
       <c r="C2" t="n">
-        <v>8486</v>
+        <v>6586</v>
       </c>
       <c r="D2" t="n">
-        <v>40539</v>
+        <v>16615</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3522</v>
+        <v>1544</v>
       </c>
       <c r="C3" t="n">
-        <v>3888</v>
+        <v>3727</v>
       </c>
       <c r="D3" t="n">
-        <v>13750</v>
+        <v>8671</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1710</v>
+        <v>1185</v>
       </c>
       <c r="C4" t="n">
-        <v>3607</v>
+        <v>5943</v>
       </c>
       <c r="D4" t="n">
-        <v>4723</v>
+        <v>3906</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>792</v>
+        <v>720</v>
       </c>
       <c r="C5" t="n">
-        <v>2212</v>
+        <v>5858</v>
       </c>
       <c r="D5" t="n">
-        <v>1483</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>272</v>
+        <v>316</v>
       </c>
       <c r="C6" t="n">
-        <v>1025</v>
+        <v>3099</v>
       </c>
       <c r="D6" t="n">
-        <v>792</v>
+        <v>882</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>334</v>
+        <v>866</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>299</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5427</v>
+        <v>1782</v>
       </c>
       <c r="C2" t="n">
-        <v>4789</v>
+        <v>11300</v>
       </c>
       <c r="D2" t="n">
-        <v>29872</v>
+        <v>17949</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4263</v>
+        <v>1569</v>
       </c>
       <c r="C3" t="n">
-        <v>5657</v>
+        <v>4440</v>
       </c>
       <c r="D3" t="n">
-        <v>17238</v>
+        <v>9168</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2288</v>
+        <v>1161</v>
       </c>
       <c r="C4" t="n">
-        <v>3701</v>
+        <v>4677</v>
       </c>
       <c r="D4" t="n">
-        <v>6353</v>
+        <v>4527</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1101</v>
+        <v>813</v>
       </c>
       <c r="C5" t="n">
-        <v>2982</v>
+        <v>5776</v>
       </c>
       <c r="D5" t="n">
-        <v>2091</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>491</v>
+        <v>447</v>
       </c>
       <c r="C6" t="n">
-        <v>1684</v>
+        <v>4339</v>
       </c>
       <c r="D6" t="n">
-        <v>913</v>
+        <v>967</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>719</v>
+        <v>1863</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>281</v>
+        <v>548</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4371</v>
+        <v>1692</v>
       </c>
       <c r="C2" t="n">
-        <v>12172</v>
+        <v>7141</v>
       </c>
       <c r="D2" t="n">
-        <v>26319</v>
+        <v>14248</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4016</v>
+        <v>2058</v>
       </c>
       <c r="C3" t="n">
-        <v>4502</v>
+        <v>7822</v>
       </c>
       <c r="D3" t="n">
-        <v>18018</v>
+        <v>10216</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2776</v>
+        <v>751</v>
       </c>
       <c r="C4" t="n">
-        <v>4713</v>
+        <v>8373</v>
       </c>
       <c r="D4" t="n">
-        <v>8249</v>
+        <v>4323</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1475</v>
+        <v>413</v>
       </c>
       <c r="C5" t="n">
-        <v>3277</v>
+        <v>4252</v>
       </c>
       <c r="D5" t="n">
-        <v>2784</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>711</v>
+        <v>170</v>
       </c>
       <c r="C6" t="n">
-        <v>2350</v>
+        <v>1825</v>
       </c>
       <c r="D6" t="n">
-        <v>1115</v>
+        <v>639</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>285</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>1219</v>
+        <v>537</v>
       </c>
       <c r="D7" t="n">
-        <v>612</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>497</v>
+        <v>277</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -6504,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>149</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
